--- a/docs/非凸α-功能部署矩阵.xlsx
+++ b/docs/非凸α-功能部署矩阵.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能部署矩阵" sheetId="1" r:id="Rf3c7290edee049b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能部署矩阵" sheetId="1" r:id="Rb0973f8af3434742"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/docs/非凸α-功能部署矩阵.xlsx
+++ b/docs/非凸α-功能部署矩阵.xlsx
@@ -2,7 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能部署矩阵" sheetId="1" r:id="Rb0973f8af3434742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怎么用" sheetId="1" r:id="R3171bb1c0dfa4a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前已部署" sheetId="2" r:id="Rcaffeeb0a24349d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="扩展能力" sheetId="3" r:id="R51653a1449fa4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="二开建议" sheetId="4" r:id="R9071cb47d32f4238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整矩阵" sheetId="5" r:id="R415a075a862a4fc0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,28 +17,156 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="444444"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.35"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="9">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -190,389 +322,982 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43.560001373291016" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="2" t="str">
+        <x:v>功能部署矩阵怎么用</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>你要先看“当前已部署”，那才是这台机器现在能直接接的能力；“扩展能力”只能当路线图或后续项目，不要混入当前默认链路。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>读表规则</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>判断问题</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>看哪一列/哪一页</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>这个功能现在能不能直接接</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>当前已部署</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>只有 onboard_deployed=yes 的功能，才算当前机器已部署。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>这个功能为什么没进主文档</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>扩展能力</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>这里单列 Elastic/FUEL/Formation/YOLO 等非当前主链能力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>我该怎么验证它真的活着</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>完整矩阵中的 verification_method</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>每行都保留了实际验证方法。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>我要追溯证据</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>完整矩阵 + 证据索引</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>需要回源码或知识库时，再看原始矩阵。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>当前机器的结论</x:v>
+      </x:c>
+      <x:c r="B12" s="6"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>结论</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>含义</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>对开发的影响</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>单机 LIO / VIO 是主链</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>当前机器真的能跑的主路径</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>二开优先围绕它们设计接口，不要被产品线文档带偏。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>Elastic / FUEL / Formation / YOLO 不是当前默认能力</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>它们只能算扩展方向</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>不要把这些能力写进当前日常使用和接口对接主流程。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>多点任务和自动起降已经落地</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>当前上层系统有现成动作原语可接</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>先把高层桥接建立起来，再考虑深改算法层。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="31.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.3799991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>当前已部署</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这里的功能才应该进入当前机器的速查和开发主路径。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>当前已部署功能</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>功能</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>可直接运行</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>入口</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>怎么验证</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>硬件依赖</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>单机 LIO</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>sh_files/run_single_lio.sh</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>启动后检查 /ekf/ekf_odom 和 /laserMapping/cloud_registered</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Livox MID360 + PX4 + Jetson</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Ego/规划主链之一</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>单机 VIO</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>sh_files/run_single_vio.sh</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>启动后检查 /vins/imu_propagate 和相机图像 topic</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>D435 + PX4 + Jetson</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>当前视觉定位主链</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>单机规划</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>diff_planner + multipoint</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>检查 /drone_0_planning/trajectory 与 /setpoints_cmd</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>LIO 或 VIO 任一定位链</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>当前主路径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>多点任务</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>multipointplan_exp_lio.launch 或 multipointplan_exp_vio.launch</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>修改 points.yaml 后触发 /move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>定位链 + multipoint</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>当前主路径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>自动起降</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land 或遥控器 8 通</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>起飞命令 1 降落命令 2</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>px4ctrl + mavros + RC</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>动作原语层</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>状态观测</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>/mavros/state /mavros/battery /ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>rostopic echo 关键状态接口</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>mavros + 定位链</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>当前主路径</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>扩展能力</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这些能力可以作为后续路线图，但不该混入当前机器默认链路。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>当前不应写入主路径的能力</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>功能</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>当前状态</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>为什么现在不算机上能力</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>需要补什么</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>入口/备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>Elastic / 目标跟踪</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>产品线文档提到，但当前机上未落地</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>仅作为后续扩展需求</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>单目相机 + apriltag / usb_cam</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>FUEL / 自主探索</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>产品线文档提到，但当前机上未落地</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>仅作为后续扩展需求</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>探索工作空间与相关依赖</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>Formation / 集群</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>源码片段存在，但非实机主链</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>源码片段存在但非实机主链</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>多机网络 + formation_ws</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>swarm_bridge 仅部分源码</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>YOLO 检测</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>产品线文档提到，但当前机上未落地</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>仅作为后续扩展需求</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>模型文件 + 检测工作空间</x:v>
+      </x:c>
+      <x:c r="E9" s="17" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38.650001525878906" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38.650001525878906" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>二开建议</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这一页把“当前已部署”和“后续扩展”之间的边界讲明白。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>建议按这个顺序做</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>开发目标</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>建议</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>不要这么做</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>接上层系统</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>先围绕单机 LIO/VIO、状态观测、多点任务、自动起降建闭环。</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>不要一开始就把 Elastic 或集群写成当前默认能力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>做任务层改造</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>优先改航点来源和动作触发层。</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>不要直接从 /setpoints_cmd 或 px4ctrl 状态机下手。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="15" t="str">
+        <x:v>做扩展规划</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>把 Elastic/FUEL/Formation/YOLO 放到独立路线图和后续验证任务里。</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>不要和当前实机主链混写在一页速查表里。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.109999656677246" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>完整矩阵</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这里保留完整原始字段。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>完整矩阵</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
         <x:v>feature_name</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>wiki_or_pdf_mentioned</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>repo_source_present</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>onboard_deployed</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>directly_runnable</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>required_hardware</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>primary_entrypoint</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H5" s="9" t="str">
         <x:v>verification_method</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I5" s="9" t="str">
         <x:v>include_in_main_quickref</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J5" s="9" t="str">
         <x:v>notes</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K5" s="9" t="str">
         <x:v>evidence_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
         <x:v>单机 LIO</x:v>
       </x:c>
-      <x:c r="B2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="B6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
         <x:v>Livox MID360 + PX4 + Jetson</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G6" s="11" t="str">
         <x:v>sh_files/run_single_lio.sh</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>启动后检查 /ekf/ekf_odom 和 /laserMapping/cloud_registered</x:v>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="I6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
         <x:v>Ego/规划主链之一</x:v>
       </x:c>
-      <x:c r="K2" t="str">
+      <x:c r="K6" s="12" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
         <x:v>单机 VIO</x:v>
       </x:c>
-      <x:c r="B3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="B7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
         <x:v>D435 + PX4 + Jetson</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G7" s="3" t="str">
         <x:v>sh_files/run_single_vio.sh</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>启动后检查 /vins/imu_propagate 和相机图像 topic</x:v>
       </x:c>
-      <x:c r="I3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="I7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="str">
         <x:v>当前视觉定位主链</x:v>
       </x:c>
-      <x:c r="K3" t="str">
+      <x:c r="K7" s="14" t="str">
         <x:v>E007_run_single_vio_script</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
         <x:v>单机规划</x:v>
       </x:c>
-      <x:c r="B4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="B8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
         <x:v>LIO 或 VIO 任一定位链</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G8" s="3" t="str">
         <x:v>diff_planner + multipoint</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>检查 /drone_0_planning/trajectory 与 /setpoints_cmd</x:v>
       </x:c>
-      <x:c r="I4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
+      <x:c r="I8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="str">
         <x:v>当前主路径</x:v>
       </x:c>
-      <x:c r="K4" t="str">
+      <x:c r="K8" s="14" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
         <x:v>多点任务</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="B9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
         <x:v>定位链 + multipoint</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="G9" s="3" t="str">
         <x:v>multipointplan_exp_lio.launch 或 multipointplan_exp_vio.launch</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>修改 points.yaml 后触发 /move_base_simple/goal</x:v>
       </x:c>
-      <x:c r="I5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
+      <x:c r="I9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="str">
         <x:v>当前主路径</x:v>
       </x:c>
-      <x:c r="K5" t="str">
+      <x:c r="K9" s="14" t="str">
         <x:v>E015_points_yaml</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
         <x:v>自动起降</x:v>
       </x:c>
-      <x:c r="B6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="B10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
         <x:v>px4ctrl + mavros + RC</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="G10" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land 或遥控器 8 通</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>起飞命令 1 降落命令 2</x:v>
       </x:c>
-      <x:c r="I6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
+      <x:c r="I10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
         <x:v>动作原语层</x:v>
       </x:c>
-      <x:c r="K6" t="str">
+      <x:c r="K10" s="14" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
         <x:v>状态观测</x:v>
       </x:c>
-      <x:c r="B7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="B11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
         <x:v>mavros + 定位链</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G11" s="3" t="str">
         <x:v>/mavros/state /mavros/battery /ekf/ekf_odom</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>rostopic echo 关键状态接口</x:v>
       </x:c>
-      <x:c r="I7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
+      <x:c r="I11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
         <x:v>当前主路径</x:v>
       </x:c>
-      <x:c r="K7" t="str">
+      <x:c r="K11" s="14" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
         <x:v>Elastic / 目标跟踪</x:v>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
+      <x:c r="B12" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
         <x:v>单目相机 + apriltag / usb_cam</x:v>
       </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="G12" s="3" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="H12" s="3" t="str">
         <x:v>仅能在 wiki/PDF 中看到流程</x:v>
       </x:c>
-      <x:c r="I8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
+      <x:c r="I12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
         <x:v>仅作为后续扩展需求</x:v>
       </x:c>
-      <x:c r="K8" t="str">
+      <x:c r="K12" s="14" t="str">
         <x:v>E010_elastic_not_onboard</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
         <x:v>FUEL / 自主探索</x:v>
       </x:c>
-      <x:c r="B9" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
+      <x:c r="B13" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
         <x:v>探索工作空间与相关依赖</x:v>
       </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="G13" s="3" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="H13" s="3" t="str">
         <x:v>当前仓库和实机都无主入口</x:v>
       </x:c>
-      <x:c r="I9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
+      <x:c r="I13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
         <x:v>仅作为后续扩展需求</x:v>
       </x:c>
-      <x:c r="K9" t="str">
+      <x:c r="K13" s="14" t="str">
         <x:v>E003_diff_planner_only_workspace</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
         <x:v>Formation / 集群</x:v>
       </x:c>
-      <x:c r="B10" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="B14" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
         <x:v>partial</x:v>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="D14" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
         <x:v>多机网络 + formation_ws</x:v>
       </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="G14" s="3" t="str">
         <x:v>swarm_bridge 仅部分源码</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="H14" s="3" t="str">
         <x:v>需要额外工作空间和网络配置</x:v>
       </x:c>
-      <x:c r="I10" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
+      <x:c r="I14" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
         <x:v>源码片段存在但非实机主链</x:v>
       </x:c>
-      <x:c r="K10" t="str">
+      <x:c r="K14" s="14" t="str">
         <x:v>E003_diff_planner_only_workspace</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
+    <x:row r="15">
+      <x:c r="A15" s="15" t="str">
         <x:v>YOLO 检测</x:v>
       </x:c>
-      <x:c r="B11" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="B15" s="16" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str">
         <x:v>模型文件 + 检测工作空间</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G15" s="16" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="H15" s="16" t="str">
         <x:v>当前仓库未提供可直接启动入口</x:v>
       </x:c>
-      <x:c r="I11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
+      <x:c r="I15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="str">
         <x:v>仅作为后续扩展需求</x:v>
       </x:c>
-      <x:c r="K11" t="str">
+      <x:c r="K15" s="17" t="str">
         <x:v>E003_diff_planner_only_workspace</x:v>
       </x:c>
     </x:row>

--- a/docs/非凸α-功能部署矩阵.xlsx
+++ b/docs/非凸α-功能部署矩阵.xlsx
@@ -2,7 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能部署矩阵" sheetId="1" r:id="Rb0973f8af3434742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怎么用" sheetId="1" r:id="R2621de379fec4d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前已部署" sheetId="2" r:id="Rdb2b12b98ac24dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="扩展能力" sheetId="3" r:id="R7bf8d2610d384ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="二开建议" sheetId="4" r:id="R5cc5501155684e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整矩阵" sheetId="5" r:id="R19ef9305245b4340"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,28 +17,156 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="444444"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.35"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="9">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -190,389 +322,982 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43.560001373291016" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="2" t="str">
+        <x:v>功能部署矩阵怎么用</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>你要先看“当前已部署”，那才是这台机器现在能直接接的能力；“扩展能力”只能当路线图或后续项目，不要混入当前默认链路。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>读表规则</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>判断问题</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>看哪一列/哪一页</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>解释</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>这个功能现在能不能直接接</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>当前已部署</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>只有 onboard_deployed=yes 的功能，才算当前机器已部署。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>这个功能为什么没进主文档</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>扩展能力</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>这里单列 Elastic/FUEL/Formation/YOLO 等非当前主链能力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>我该怎么验证它真的活着</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>完整矩阵中的 verification_method</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>每行都保留了实际验证方法。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>我要追溯证据</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>完整矩阵 + 证据索引</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>需要回源码或知识库时，再看原始矩阵。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>当前机器的结论</x:v>
+      </x:c>
+      <x:c r="B12" s="6"/>
+      <x:c r="C12" s="6"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>结论</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>含义</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>对开发的影响</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>单机 LIO / VIO 是主链</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>当前机器真的能跑的主路径</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>二开优先围绕它们设计接口，不要被产品线文档带偏。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>Elastic / FUEL / Formation / YOLO 不是当前默认能力</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>它们只能算扩展方向</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>不要把这些能力写进当前日常使用和接口对接主流程。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>多点任务和自动起降已经落地</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>当前上层系统有现成动作原语可接</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>先把高层桥接建立起来，再考虑深改算法层。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="31.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.3799991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>当前已部署</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这里的功能才应该进入当前机器的速查和开发主路径。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>当前已部署功能</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>功能</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>可直接运行</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>入口</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>怎么验证</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>硬件依赖</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>单机 LIO</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>sh_files/run_single_lio.sh</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>启动后检查 /ekf/ekf_odom 和 /laserMapping/cloud_registered</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Livox MID360 + PX4 + Jetson</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Ego/规划主链之一</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>单机 VIO</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>sh_files/run_single_vio.sh</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>启动后检查 /vins/imu_propagate 和相机图像 topic</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>D435 + PX4 + Jetson</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>当前视觉定位主链</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>单机规划</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>diff_planner + multipoint</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>检查 /drone_0_planning/trajectory 与 /setpoints_cmd</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>LIO 或 VIO 任一定位链</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>当前主路径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>多点任务</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>multipointplan_exp_lio.launch 或 multipointplan_exp_vio.launch</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>修改 points.yaml 后触发 /move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>定位链 + multipoint</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>当前主路径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>自动起降</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land 或遥控器 8 通</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>起飞命令 1 降落命令 2</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>px4ctrl + mavros + RC</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>动作原语层</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>状态观测</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>/mavros/state /mavros/battery /ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>rostopic echo 关键状态接口</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>mavros + 定位链</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>当前主路径</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>扩展能力</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这些能力可以作为后续路线图，但不该混入当前机器默认链路。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>当前不应写入主路径的能力</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>功能</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>当前状态</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>为什么现在不算机上能力</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>需要补什么</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>入口/备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>Elastic / 目标跟踪</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>产品线文档提到，但当前机上未落地</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>仅作为后续扩展需求</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>单目相机 + apriltag / usb_cam</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>FUEL / 自主探索</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>产品线文档提到，但当前机上未落地</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>仅作为后续扩展需求</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>探索工作空间与相关依赖</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>Formation / 集群</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>源码片段存在，但非实机主链</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>源码片段存在但非实机主链</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>多机网络 + formation_ws</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>swarm_bridge 仅部分源码</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>YOLO 检测</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>产品线文档提到，但当前机上未落地</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>仅作为后续扩展需求</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>模型文件 + 检测工作空间</x:v>
+      </x:c>
+      <x:c r="E9" s="17" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38.650001525878906" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38.650001525878906" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>二开建议</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这一页把“当前已部署”和“后续扩展”之间的边界讲明白。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>建议按这个顺序做</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>开发目标</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>建议</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>不要这么做</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>接上层系统</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>先围绕单机 LIO/VIO、状态观测、多点任务、自动起降建闭环。</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>不要一开始就把 Elastic 或集群写成当前默认能力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>做任务层改造</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>优先改航点来源和动作触发层。</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>不要直接从 /setpoints_cmd 或 px4ctrl 状态机下手。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="15" t="str">
+        <x:v>做扩展规划</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>把 Elastic/FUEL/Formation/YOLO 放到独立路线图和后续验证任务里。</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>不要和当前实机主链混写在一页速查表里。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.109999656677246" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>完整矩阵</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这里保留完整原始字段。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>完整矩阵</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
         <x:v>feature_name</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>wiki_or_pdf_mentioned</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>repo_source_present</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>onboard_deployed</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>directly_runnable</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>required_hardware</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>primary_entrypoint</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H5" s="9" t="str">
         <x:v>verification_method</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I5" s="9" t="str">
         <x:v>include_in_main_quickref</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J5" s="9" t="str">
         <x:v>notes</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K5" s="9" t="str">
         <x:v>evidence_id</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
         <x:v>单机 LIO</x:v>
       </x:c>
-      <x:c r="B2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="B6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
         <x:v>Livox MID360 + PX4 + Jetson</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G6" s="11" t="str">
         <x:v>sh_files/run_single_lio.sh</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>启动后检查 /ekf/ekf_odom 和 /laserMapping/cloud_registered</x:v>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="I6" s="11" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
         <x:v>Ego/规划主链之一</x:v>
       </x:c>
-      <x:c r="K2" t="str">
+      <x:c r="K6" s="12" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
         <x:v>单机 VIO</x:v>
       </x:c>
-      <x:c r="B3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="B7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
         <x:v>D435 + PX4 + Jetson</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G7" s="3" t="str">
         <x:v>sh_files/run_single_vio.sh</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>启动后检查 /vins/imu_propagate 和相机图像 topic</x:v>
       </x:c>
-      <x:c r="I3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="I7" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="str">
         <x:v>当前视觉定位主链</x:v>
       </x:c>
-      <x:c r="K3" t="str">
+      <x:c r="K7" s="14" t="str">
         <x:v>E007_run_single_vio_script</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
         <x:v>单机规划</x:v>
       </x:c>
-      <x:c r="B4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="B8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
         <x:v>LIO 或 VIO 任一定位链</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G8" s="3" t="str">
         <x:v>diff_planner + multipoint</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>检查 /drone_0_planning/trajectory 与 /setpoints_cmd</x:v>
       </x:c>
-      <x:c r="I4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
+      <x:c r="I8" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="str">
         <x:v>当前主路径</x:v>
       </x:c>
-      <x:c r="K4" t="str">
+      <x:c r="K8" s="14" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
         <x:v>多点任务</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="B9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
         <x:v>定位链 + multipoint</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="G9" s="3" t="str">
         <x:v>multipointplan_exp_lio.launch 或 multipointplan_exp_vio.launch</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>修改 points.yaml 后触发 /move_base_simple/goal</x:v>
       </x:c>
-      <x:c r="I5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
+      <x:c r="I9" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="str">
         <x:v>当前主路径</x:v>
       </x:c>
-      <x:c r="K5" t="str">
+      <x:c r="K9" s="14" t="str">
         <x:v>E015_points_yaml</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
         <x:v>自动起降</x:v>
       </x:c>
-      <x:c r="B6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="B10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
         <x:v>px4ctrl + mavros + RC</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="G10" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land 或遥控器 8 通</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>起飞命令 1 降落命令 2</x:v>
       </x:c>
-      <x:c r="I6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
+      <x:c r="I10" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
         <x:v>动作原语层</x:v>
       </x:c>
-      <x:c r="K6" t="str">
+      <x:c r="K10" s="14" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
         <x:v>状态观测</x:v>
       </x:c>
-      <x:c r="B7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="B11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
         <x:v>mavros + 定位链</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G11" s="3" t="str">
         <x:v>/mavros/state /mavros/battery /ekf/ekf_odom</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>rostopic echo 关键状态接口</x:v>
       </x:c>
-      <x:c r="I7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
+      <x:c r="I11" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
         <x:v>当前主路径</x:v>
       </x:c>
-      <x:c r="K7" t="str">
+      <x:c r="K11" s="14" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
         <x:v>Elastic / 目标跟踪</x:v>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
+      <x:c r="B12" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
         <x:v>单目相机 + apriltag / usb_cam</x:v>
       </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="G12" s="3" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="H12" s="3" t="str">
         <x:v>仅能在 wiki/PDF 中看到流程</x:v>
       </x:c>
-      <x:c r="I8" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
+      <x:c r="I12" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
         <x:v>仅作为后续扩展需求</x:v>
       </x:c>
-      <x:c r="K8" t="str">
+      <x:c r="K12" s="14" t="str">
         <x:v>E010_elastic_not_onboard</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
         <x:v>FUEL / 自主探索</x:v>
       </x:c>
-      <x:c r="B9" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
+      <x:c r="B13" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
         <x:v>探索工作空间与相关依赖</x:v>
       </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="G13" s="3" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="H13" s="3" t="str">
         <x:v>当前仓库和实机都无主入口</x:v>
       </x:c>
-      <x:c r="I9" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
+      <x:c r="I13" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
         <x:v>仅作为后续扩展需求</x:v>
       </x:c>
-      <x:c r="K9" t="str">
+      <x:c r="K13" s="14" t="str">
         <x:v>E003_diff_planner_only_workspace</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
         <x:v>Formation / 集群</x:v>
       </x:c>
-      <x:c r="B10" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="B14" s="3" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
         <x:v>partial</x:v>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="D14" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
         <x:v>多机网络 + formation_ws</x:v>
       </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="G14" s="3" t="str">
         <x:v>swarm_bridge 仅部分源码</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="H14" s="3" t="str">
         <x:v>需要额外工作空间和网络配置</x:v>
       </x:c>
-      <x:c r="I10" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
+      <x:c r="I14" s="3" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
         <x:v>源码片段存在但非实机主链</x:v>
       </x:c>
-      <x:c r="K10" t="str">
+      <x:c r="K14" s="14" t="str">
         <x:v>E003_diff_planner_only_workspace</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
+    <x:row r="15">
+      <x:c r="A15" s="15" t="str">
         <x:v>YOLO 检测</x:v>
       </x:c>
-      <x:c r="B11" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="B15" s="16" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str">
         <x:v>模型文件 + 检测工作空间</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G15" s="16" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="H15" s="16" t="str">
         <x:v>当前仓库未提供可直接启动入口</x:v>
       </x:c>
-      <x:c r="I11" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
+      <x:c r="I15" s="16" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="str">
         <x:v>仅作为后续扩展需求</x:v>
       </x:c>
-      <x:c r="K11" t="str">
+      <x:c r="K15" s="17" t="str">
         <x:v>E003_diff_planner_only_workspace</x:v>
       </x:c>
     </x:row>
